--- a/nriss-patch-1/ig/CodeSystem-fr-core-cs-location-position-lit.xlsx
+++ b/nriss-patch-1/ig/CodeSystem-fr-core-cs-location-position-lit.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:55:04+00:00</t>
+    <t>2026-02-24T08:54:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -504,7 +504,9 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -528,7 +530,9 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/nriss-patch-1/ig/CodeSystem-fr-core-cs-location-position-lit.xlsx
+++ b/nriss-patch-1/ig/CodeSystem-fr-core-cs-location-position-lit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T10:29:07+00:00</t>
+    <t>2026-06-05T13:13:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
